--- a/data/trans_bre/POLIPATOLOGIA_5-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,12</t>
+          <t>-0,72; 5,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,54</t>
+          <t>1,92; 7,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,67</t>
+          <t>-2,24; 4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,23</t>
+          <t>0,41; 6,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 306,75</t>
+          <t>-27,63; 314,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 138,54</t>
+          <t>-45,13; 187,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 132,39</t>
+          <t>4,44; 128,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,21</t>
+          <t>-0,74; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,23</t>
+          <t>0,41; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,82</t>
+          <t>0,42; 5,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,38</t>
+          <t>2,1; 8,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 354,49</t>
+          <t>-32,94; 343,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 604,56</t>
+          <t>4,61; 556,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 806,37</t>
+          <t>-2,74; 1037,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,02; 152,74</t>
+          <t>23,28; 152,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,97</t>
+          <t>1,11; 10,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,22</t>
+          <t>-1,51; 5,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,89</t>
+          <t>6,31; 19,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 22,27</t>
+          <t>7,66; 22,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,14; 460,59</t>
+          <t>21,55; 414,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 141,13</t>
+          <t>-28,53; 159,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>171,79; 993,54</t>
+          <t>165,16; 987,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,17; 749,61</t>
+          <t>69,47; 759,65</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,59</t>
+          <t>-0,44; 3,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,98</t>
+          <t>-1,58; 3,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,39</t>
+          <t>1,1; 5,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 53,55</t>
+          <t>0,42; 47,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 93,11</t>
+          <t>-8,94; 98,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,52; 57,17</t>
+          <t>-23,65; 61,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,47; 173,45</t>
+          <t>23,82; 178,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 571,5</t>
+          <t>3,45; 490,22</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,91</t>
+          <t>-0,84; 5,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,8</t>
+          <t>6,81; 12,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,27</t>
+          <t>4,03; 10,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 17,45</t>
+          <t>7,69; 18,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 160,82</t>
+          <t>-14,69; 160,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>130,4; 513,18</t>
+          <t>125,64; 488,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,68; 206,52</t>
+          <t>55,07; 218,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,68; 215,03</t>
+          <t>68,45; 223,87</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,52</t>
+          <t>6,33; 9,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,21</t>
+          <t>10,26; 15,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,13</t>
+          <t>9,88; 14,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,3; 19,53</t>
+          <t>14,46; 19,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>440,41; —</t>
+          <t>438,56; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>402,51; 2504,95</t>
+          <t>398,62; 2266,58</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,39</t>
+          <t>2,25; 4,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,29</t>
+          <t>4,78; 7,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,42</t>
+          <t>5,05; 7,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,77; 27,72</t>
+          <t>7,68; 27,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,04; 147,59</t>
+          <t>57,29; 144,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>109,42; 220,1</t>
+          <t>110,8; 220,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>121,75; 238,46</t>
+          <t>124,98; 244,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,68; 386,24</t>
+          <t>89,72; 344,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_5-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,28</t>
+          <t>-0,79; 4,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,38</t>
+          <t>1,94; 7,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,0</t>
+          <t>-2,29; 3,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,03</t>
+          <t>0,51; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 314,53</t>
+          <t>-27,59; 299,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 187,35</t>
+          <t>-45,69; 162,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 128,58</t>
+          <t>5,46; 128,09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,34</t>
+          <t>-0,67; 4,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,98</t>
+          <t>0,36; 6,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,87</t>
+          <t>0,19; 5,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,68</t>
+          <t>2,3; 8,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 343,14</t>
+          <t>-29,01; 298,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 556,37</t>
+          <t>-2,11; 507,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1037,14</t>
+          <t>-18,23; 922,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,28; 152,82</t>
+          <t>25,83; 167,71</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,45</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>194,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,77</t>
+          <t>1,26; 10,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 5,39</t>
+          <t>-1,68; 5,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 19,09</t>
+          <t>6,39; 18,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 22,69</t>
+          <t>4,0; 14,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,55; 414,71</t>
+          <t>20,83; 432,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 159,22</t>
+          <t>-31,87; 153,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165,16; 987,53</t>
+          <t>154,01; 900,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,47; 759,65</t>
+          <t>32,39; 168,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,65</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>183,18%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,79</t>
+          <t>-0,59; 3,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,17</t>
+          <t>-1,54; 3,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,5</t>
+          <t>1,35; 5,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 47,03</t>
+          <t>-0,74; 4,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 98,97</t>
+          <t>-11,44; 92,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 61,67</t>
+          <t>-22,68; 61,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,82; 178,9</t>
+          <t>30,25; 171,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 490,22</t>
+          <t>-6,69; 43,61</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>16,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>133,02%</t>
+          <t>185,75%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 5,25</t>
+          <t>-1,23; 4,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,99</t>
+          <t>7,24; 12,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,35</t>
+          <t>4,16; 10,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 18,09</t>
+          <t>12,86; 19,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 160,5</t>
+          <t>-21,35; 140,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>125,64; 488,64</t>
+          <t>132,24; 505,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,07; 218,54</t>
+          <t>54,02; 204,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,45; 223,87</t>
+          <t>119,14; 272,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>926,46%</t>
+          <t>624,23%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,76</t>
+          <t>6,11; 9,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 15,16</t>
+          <t>10,58; 15,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,3</t>
+          <t>9,83; 14,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,46; 19,51</t>
+          <t>12,47; 18,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>438,56; —</t>
+          <t>453,03; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>398,62; 2266,58</t>
+          <t>227,91; 1510,2</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,13</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>163,98%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,25</t>
+          <t>2,18; 4,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,26</t>
+          <t>4,85; 7,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 7,61</t>
+          <t>4,97; 7,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 27,9</t>
+          <t>6,76; 9,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,29; 144,41</t>
+          <t>56,34; 143,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>110,8; 220,79</t>
+          <t>110,16; 217,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>124,98; 244,68</t>
+          <t>122,28; 239,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,72; 344,54</t>
+          <t>72,82; 120,36</t>
         </is>
       </c>
     </row>
